--- a/branches/Richard/StructureDefinition-viral-load-log.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-log.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:06:08+00:00</t>
+    <t>2023-05-08T19:17:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-log.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-log.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:17:16+00:00</t>
+    <t>2023-05-08T19:36:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-log.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-log.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:36:32+00:00</t>
+    <t>2023-05-08T19:37:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-log.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-log.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:37:24+00:00</t>
+    <t>2023-05-08T19:39:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-log.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-log.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:39:41+00:00</t>
+    <t>2023-05-08T19:40:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-log.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-log.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:40:43+00:00</t>
+    <t>2023-05-08T19:42:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-log.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-log.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:42:22+00:00</t>
+    <t>2023-05-08T19:53:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-log.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-log.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:53:59+00:00</t>
+    <t>2023-05-08T21:00:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-log.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-log.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T21:00:30+00:00</t>
+    <t>2023-05-08T21:01:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-log.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-log.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2494" uniqueCount="526">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2493" uniqueCount="528">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T21:01:17+00:00</t>
+    <t>2023-05-09T15:00:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -93,7 +93,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.0.1</t>
+    <t>4.3.0</t>
   </si>
   <si>
     <t>Kind</t>
@@ -290,6 +290,9 @@
     <t>Observation[classCode=OBS, moodCode=EVN]</t>
   </si>
   <si>
+    <t>clinical.diagnostics</t>
+  </si>
+  <si>
     <t>Observation.id</t>
   </si>
   <si>
@@ -373,7 +376,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>A human language.</t>
+    <t>IETF language tag</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages</t>
@@ -431,6 +434,10 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
+    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
+</t>
+  </si>
+  <si>
     <t>N/A</t>
   </si>
   <si>
@@ -471,7 +478,7 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -551,7 +558,7 @@
     <t>A larger event of which this particular Observation is a component or step.  For example,  an observation as part of a procedure.</t>
   </si>
   <si>
-    <t>To link an Observation to an Encounter use `encounter`.  See the  [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below for guidance on referencing another Observation.</t>
+    <t>To link an Observation to an Encounter use `encounter`.  See the  [Notes](http://hl7.org/fhir/R4B/observation.html#obsgrouping) below for guidance on referencing another Observation.</t>
   </si>
   <si>
     <t>Event.partOf</t>
@@ -584,7 +591,7 @@
     <t>Codes providing the status of an observation.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-status|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-status|4.3.0</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -676,72 +683,72 @@
     <t>Observation.code.id</t>
   </si>
   <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Observation.code.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Observation.code.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>Observation.code.text</t>
+  </si>
+  <si>
     <t xml:space="preserve">string
 </t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>Observation.code.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>Observation.code.coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>Observation.code.text</t>
-  </si>
-  <si>
     <t>Plain text representation of the concept</t>
   </si>
   <si>
@@ -769,7 +776,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Group|Device|Location)
+    <t xml:space="preserve">Reference(Patient|Group|Device|Location|Organization|Procedure|Practitioner|Medication|Substance)
 </t>
   </si>
   <si>
@@ -810,7 +817,7 @@
     <t>The actual focus of an observation when it is not the patient of record representing something or someone associated with the patient such as a spouse, parent, fetus, or donor. For example, fetus observations in a mother's record.  The focus of an observation could also be an existing condition,  an intervention, the subject's diet,  another observation of the subject,  or a body structure such as tumor or implanted device.   An example use case would be using the Observation resource to capture whether the mother is trained to change her child's tracheostomy tube. In this example, the child is the patient of record and the mother is the focus.</t>
   </si>
   <si>
-    <t>Typically, an observation is made about the subject - a patient, or group of patients, location, or device - and the distinction between the subject and what is directly measured for an observation is specified in the observation code itself ( e.g., "Blood Glucose") and does not need to be represented separately using this element.  Use `specimen` if a reference to a specimen is required.  If a code is required instead of a resource use either  `bodysite` for bodysites or the standard extension [focusCode](http://hl7.org/fhir/R4/extension-observation-focuscode.html).</t>
+    <t>Typically, an observation is made about the subject - a patient, or group of patients, location, or device - and the distinction between the subject and what is directly measured for an observation is specified in the observation code itself ( e.g., "Blood Glucose") and does not need to be represented separately using this element.  Use `specimen` if a reference to a specimen is required.  If a code is required instead of a resource use either  `bodysite` for bodysites or the standard extension [focusCode](http://hl7.org/fhir/R4B/extension-observation-focuscode.html).</t>
   </si>
   <si>
     <t>participation[typeCode=SBJ]</t>
@@ -868,7 +875,7 @@
     <t>The time or time-period the observed value is asserted as being true. For biological subjects - e.g. human patients - this is usually called the "physiologically relevant time". This is usually either the time of the procedure or of specimen collection, but very often the source of the date/time is not known, only the date/time itself.</t>
   </si>
   <si>
-    <t>At least a date should be present unless this observation is a historical report.  For recording imprecise or "fuzzy" times (For example, a blood glucose measurement taken "after breakfast") use the [Timing](http://hl7.org/fhir/R4/datatypes.html#timing) datatype which allow the measurement to be tied to regular life events.</t>
+    <t>At least a date should be present unless this observation is a historical report.  For recording imprecise or "fuzzy" times (For example, a blood glucose measurement taken "after breakfast") use the [Timing](http://hl7.org/fhir/R4B/datatypes.html#timing) datatype which allow the measurement to be tied to regular life events.</t>
   </si>
   <si>
     <t>Knowing when an observation was deemed true is important to its relevance as well as determining trends.</t>
@@ -912,7 +919,7 @@
     <t>The date and time this version of the observation was made available to providers, typically after the results have been reviewed and verified.</t>
   </si>
   <si>
-    <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/R4/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
+    <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/R4B/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
   </si>
   <si>
     <t>OBR.22 (or MSH.7), or perhaps OBX-19 (depends on who observation made)</t>
@@ -965,7 +972,7 @@
     <t>The information determined as a result of making the observation, if the information has a simple value.</t>
   </si>
   <si>
-    <t>An observation may have; 1)  a single value here, 2)  both a value and a set of related or component values,  or 3)  only a set of related or component values. If a value is present, the datatype for this element should be determined by Observation.code.  A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
+    <t>An observation may have; 1)  a single value here, 2)  both a value and a set of related or component values,  or 3)  only a set of related or component values. If a value is present, the datatype for this element should be determined by Observation.code.  A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4B/observation.html#notes) below.</t>
   </si>
   <si>
     <t>An observation exists to have a value, though it might not if it is in error, or if it represents a group of observations.</t>
@@ -1054,10 +1061,7 @@
     <t>If there is no comparator, then there is no modification of the value</t>
   </si>
   <si>
-    <t>How the Quantity should be understood and represented.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/quantity-comparator|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/quantity-comparator|4.3.0</t>
   </si>
   <si>
     <t>Quantity.comparator</t>
@@ -1246,13 +1250,13 @@
   </si>
   <si>
     <t>Only used if not implicit in code found in Observation.code.  In many systems, this may be represented as a related observation instead of an inline component.   
-If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
+If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4B/extension-bodysite.html).</t>
   </si>
   <si>
     <t>example</t>
   </si>
   <si>
-    <t>Codes describing anatomical locations. May include laterality.</t>
+    <t>SNOMED CT Body site concepts</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/body-site</t>
@@ -1372,7 +1376,7 @@
     <t>Knowing what values are considered "normal" can help evaluate the significance of a particular result. Need to be able to provide multiple reference ranges for different contexts.</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
 obs-3:Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
   </si>
   <si>
@@ -1538,7 +1542,7 @@
     <t>This observation is a group observation (e.g. a battery, a panel of tests, a set of vital sign measurements) that includes the target as a member of the group.</t>
   </si>
   <si>
-    <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](http://hl7.org/fhir/R4/questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
+    <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4B/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](http://hl7.org/fhir/R4B/questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
   </si>
   <si>
     <t>Relationships established by OBX-4 usage</t>
@@ -1560,7 +1564,7 @@
     <t>The target resource that represents a measurement from which this observation value is derived. For example, a calculated anion gap or a fetal measurement based on an ultrasound image.</t>
   </si>
   <si>
-    <t>All the reference choices that are listed in this element can represent clinical observations and other measurements that may be the source for a derived value.  The most common reference will be another Observation.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.</t>
+    <t>All the reference choices that are listed in this element can represent clinical observations and other measurements that may be the source for a derived value.  The most common reference will be another Observation.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4B/observation.html#obsgrouping) below.</t>
   </si>
   <si>
     <t>.targetObservation</t>
@@ -1575,10 +1579,14 @@
     <t>Some observations have multiple component observations.  These component observations are expressed as separate code value pairs that share the same attributes.  Examples include systolic and diastolic component observations for blood pressure measurement and multiple component observations for genetics observations.</t>
   </si>
   <si>
-    <t>For a discussion on the ways Observations can be assembled in groups together see [Notes](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
+    <t>For a discussion on the ways Observations can be assembled in groups together see [Notes](http://hl7.org/fhir/R4B/observation.html#notes) below.</t>
   </si>
   <si>
     <t>Component observations share the same attributes in the Observation resource as the primary observation and are always treated a part of a single observation (they are not separable).   However, the reference range for the primary observation value is not inherited by the component values and is required when appropriate for each component observation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+</t>
   </si>
   <si>
     <t>containment by OBX-4?</t>
@@ -1628,7 +1636,7 @@
     <t>Actual component result</t>
   </si>
   <si>
-    <t>Used when observation has a set of component observations. An observation may have both a value (e.g. an  Apgar score)  and component observations (the observations from which the Apgar score was derived). If a value is present, the datatype for this element should be determined by Observation.code. A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
+    <t>Used when observation has a set of component observations. An observation may have both a value (e.g. an  Apgar score)  and component observations (the observations from which the Apgar score was derived). If a value is present, the datatype for this element should be determined by Observation.code. A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4B/observation.html#notes) below.</t>
   </si>
   <si>
     <t>363714003 |Interprets| &lt; 441742003 |Evaluation finding|</t>
@@ -2261,7 +2269,7 @@
         <v>89</v>
       </c>
       <c r="AO2" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AP2" t="s" s="2">
         <v>81</v>
@@ -2269,10 +2277,10 @@
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -2283,7 +2291,7 @@
         <v>79</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>81</v>
@@ -2292,19 +2300,19 @@
         <v>81</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -2354,13 +2362,13 @@
         <v>81</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>81</v>
@@ -2389,10 +2397,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2403,7 +2411,7 @@
         <v>79</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>81</v>
@@ -2412,16 +2420,16 @@
         <v>81</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2472,19 +2480,19 @@
         <v>81</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>81</v>
@@ -2507,10 +2515,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2521,28 +2529,28 @@
         <v>79</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2592,19 +2600,19 @@
         <v>81</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>81</v>
@@ -2627,10 +2635,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2641,7 +2649,7 @@
         <v>79</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>81</v>
@@ -2653,16 +2661,16 @@
         <v>81</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2688,13 +2696,13 @@
         <v>81</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>81</v>
@@ -2712,19 +2720,19 @@
         <v>81</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>81</v>
@@ -2747,21 +2755,21 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>81</v>
@@ -2773,16 +2781,16 @@
         <v>81</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2832,19 +2840,19 @@
         <v>81</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>81</v>
@@ -2856,7 +2864,7 @@
         <v>81</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AO7" t="s" s="2">
         <v>81</v>
@@ -2867,14 +2875,14 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2893,16 +2901,16 @@
         <v>81</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2952,7 +2960,7 @@
         <v>81</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>79</v>
@@ -2964,7 +2972,7 @@
         <v>81</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>81</v>
+        <v>135</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>81</v>
@@ -2976,7 +2984,7 @@
         <v>81</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AO8" t="s" s="2">
         <v>81</v>
@@ -2987,14 +2995,14 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -3013,16 +3021,16 @@
         <v>81</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -3072,7 +3080,7 @@
         <v>81</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>79</v>
@@ -3084,7 +3092,7 @@
         <v>81</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>81</v>
@@ -3096,7 +3104,7 @@
         <v>81</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AO9" t="s" s="2">
         <v>81</v>
@@ -3107,14 +3115,14 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -3127,25 +3135,25 @@
         <v>81</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>81</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>81</v>
@@ -3194,7 +3202,7 @@
         <v>81</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>79</v>
@@ -3206,7 +3214,7 @@
         <v>81</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>81</v>
@@ -3218,7 +3226,7 @@
         <v>81</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AO10" t="s" s="2">
         <v>81</v>
@@ -3229,10 +3237,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3252,20 +3260,20 @@
         <v>81</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>81</v>
@@ -3314,7 +3322,7 @@
         <v>81</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>79</v>
@@ -3326,22 +3334,22 @@
         <v>81</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AL11" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="AO11" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AP11" t="s" s="2">
         <v>81</v>
@@ -3349,14 +3357,14 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -3372,20 +3380,20 @@
         <v>81</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>81</v>
@@ -3434,7 +3442,7 @@
         <v>81</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>79</v>
@@ -3446,19 +3454,19 @@
         <v>81</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>81</v>
@@ -3469,14 +3477,14 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -3492,19 +3500,19 @@
         <v>81</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3554,7 +3562,7 @@
         <v>81</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>79</v>
@@ -3566,19 +3574,19 @@
         <v>81</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>81</v>
@@ -3589,10 +3597,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3600,34 +3608,34 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>81</v>
@@ -3652,13 +3660,13 @@
         <v>81</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>81</v>
@@ -3676,34 +3684,34 @@
         <v>81</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AP14" t="s" s="2">
         <v>81</v>
@@ -3711,10 +3719,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3737,19 +3745,19 @@
         <v>81</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>81</v>
@@ -3774,13 +3782,13 @@
         <v>81</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>81</v>
@@ -3798,7 +3806,7 @@
         <v>81</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
@@ -3810,7 +3818,7 @@
         <v>81</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>81</v>
@@ -3822,10 +3830,10 @@
         <v>81</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>81</v>
@@ -3833,21 +3841,21 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>81</v>
@@ -3856,22 +3864,22 @@
         <v>81</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>81</v>
@@ -3896,11 +3904,11 @@
         <v>81</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>81</v>
@@ -3918,45 +3926,45 @@
         <v>81</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3967,7 +3975,7 @@
         <v>79</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>81</v>
@@ -3979,13 +3987,13 @@
         <v>81</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>212</v>
+        <v>94</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4036,13 +4044,13 @@
         <v>81</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>81</v>
@@ -4060,7 +4068,7 @@
         <v>81</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>81</v>
@@ -4071,14 +4079,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -4097,16 +4105,16 @@
         <v>81</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4144,19 +4152,19 @@
         <v>81</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -4168,7 +4176,7 @@
         <v>81</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>81</v>
@@ -4180,7 +4188,7 @@
         <v>81</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>81</v>
@@ -4191,10 +4199,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4214,22 +4222,22 @@
         <v>81</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>81</v>
@@ -4278,7 +4286,7 @@
         <v>81</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -4290,7 +4298,7 @@
         <v>81</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>81</v>
@@ -4299,10 +4307,10 @@
         <v>81</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>81</v>
@@ -4313,10 +4321,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4327,7 +4335,7 @@
         <v>79</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>81</v>
@@ -4336,22 +4344,22 @@
         <v>81</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>212</v>
+        <v>234</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>81</v>
@@ -4361,7 +4369,7 @@
         <v>81</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="T20" t="s" s="2">
         <v>81</v>
@@ -4400,19 +4408,19 @@
         <v>81</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>81</v>
@@ -4421,10 +4429,10 @@
         <v>81</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>81</v>
@@ -4435,10 +4443,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4446,10 +4454,10 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>81</v>
@@ -4458,22 +4466,22 @@
         <v>81</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>81</v>
@@ -4522,34 +4530,34 @@
         <v>81</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>81</v>
@@ -4557,10 +4565,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4580,19 +4588,19 @@
         <v>81</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4642,7 +4650,7 @@
         <v>81</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -4654,7 +4662,7 @@
         <v>81</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>81</v>
@@ -4663,13 +4671,13 @@
         <v>81</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>81</v>
@@ -4677,21 +4685,21 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>81</v>
@@ -4700,22 +4708,22 @@
         <v>81</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>81</v>
@@ -4764,34 +4772,34 @@
         <v>81</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>81</v>
@@ -4799,21 +4807,21 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>81</v>
@@ -4822,22 +4830,22 @@
         <v>81</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>81</v>
@@ -4874,44 +4882,44 @@
         <v>81</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AC24" s="2"/>
       <c r="AD24" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>81</v>
@@ -4919,23 +4927,23 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D25" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>81</v>
@@ -4944,22 +4952,22 @@
         <v>81</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>81</v>
@@ -5008,34 +5016,34 @@
         <v>81</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>81</v>
@@ -5043,10 +5051,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5057,7 +5065,7 @@
         <v>79</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>81</v>
@@ -5066,19 +5074,19 @@
         <v>81</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -5128,19 +5136,19 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>81</v>
@@ -5149,13 +5157,13 @@
         <v>81</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>81</v>
@@ -5163,10 +5171,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5174,7 +5182,7 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>80</v>
@@ -5186,20 +5194,20 @@
         <v>81</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>81</v>
@@ -5248,7 +5256,7 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -5260,22 +5268,22 @@
         <v>81</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>81</v>
@@ -5283,10 +5291,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5294,10 +5302,10 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>81</v>
@@ -5306,22 +5314,22 @@
         <v>81</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>81</v>
@@ -5358,68 +5366,68 @@
         <v>81</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AC28" s="2"/>
       <c r="AD28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="D29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>81</v>
@@ -5428,22 +5436,22 @@
         <v>81</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>81</v>
@@ -5492,45 +5500,45 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5541,7 +5549,7 @@
         <v>79</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>81</v>
@@ -5553,13 +5561,13 @@
         <v>81</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>212</v>
+        <v>94</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5610,13 +5618,13 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>81</v>
@@ -5634,7 +5642,7 @@
         <v>81</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>81</v>
@@ -5645,14 +5653,14 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5671,16 +5679,16 @@
         <v>81</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5718,19 +5726,19 @@
         <v>81</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5742,7 +5750,7 @@
         <v>81</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>81</v>
@@ -5754,7 +5762,7 @@
         <v>81</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>81</v>
@@ -5765,10 +5773,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5776,10 +5784,10 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>81</v>
@@ -5788,22 +5796,22 @@
         <v>81</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>81</v>
@@ -5852,19 +5860,19 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>81</v>
@@ -5873,10 +5881,10 @@
         <v>81</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>81</v>
@@ -5887,10 +5895,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5901,35 +5909,35 @@
         <v>79</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q33" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="R33" t="s" s="2">
         <v>81</v>
@@ -5950,13 +5958,11 @@
         <v>81</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="Y33" t="s" s="2">
-        <v>333</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="Y33" s="2"/>
       <c r="Z33" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>81</v>
@@ -5974,19 +5980,19 @@
         <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>81</v>
@@ -5995,10 +6001,10 @@
         <v>81</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>81</v>
@@ -6009,10 +6015,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6023,7 +6029,7 @@
         <v>79</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>81</v>
@@ -6032,20 +6038,20 @@
         <v>81</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>212</v>
+        <v>234</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>81</v>
@@ -6094,19 +6100,19 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>81</v>
@@ -6115,10 +6121,10 @@
         <v>81</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>81</v>
@@ -6129,10 +6135,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6143,7 +6149,7 @@
         <v>79</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>81</v>
@@ -6152,20 +6158,20 @@
         <v>81</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>81</v>
@@ -6214,19 +6220,19 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>81</v>
@@ -6235,10 +6241,10 @@
         <v>81</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>81</v>
@@ -6249,10 +6255,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6263,7 +6269,7 @@
         <v>79</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>81</v>
@@ -6272,22 +6278,22 @@
         <v>81</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>81</v>
@@ -6336,19 +6342,19 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>81</v>
@@ -6357,10 +6363,10 @@
         <v>81</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>81</v>
@@ -6371,10 +6377,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6385,7 +6391,7 @@
         <v>79</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>81</v>
@@ -6397,19 +6403,19 @@
         <v>81</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>81</v>
@@ -6434,13 +6440,13 @@
         <v>81</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>81</v>
@@ -6458,19 +6464,19 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>81</v>
@@ -6479,10 +6485,10 @@
         <v>81</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>81</v>
@@ -6493,14 +6499,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6519,19 +6525,19 @@
         <v>81</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>81</v>
@@ -6556,13 +6562,13 @@
         <v>81</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>81</v>
@@ -6580,7 +6586,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6592,33 +6598,33 @@
         <v>81</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6632,7 +6638,7 @@
         <v>80</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>81</v>
@@ -6641,19 +6647,19 @@
         <v>81</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>81</v>
@@ -6702,7 +6708,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6714,7 +6720,7 @@
         <v>81</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>81</v>
@@ -6723,10 +6729,10 @@
         <v>81</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>81</v>
@@ -6737,10 +6743,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6751,7 +6757,7 @@
         <v>79</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>81</v>
@@ -6763,16 +6769,16 @@
         <v>81</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6798,13 +6804,13 @@
         <v>81</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>81</v>
@@ -6822,45 +6828,45 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6871,7 +6877,7 @@
         <v>79</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>81</v>
@@ -6883,19 +6889,19 @@
         <v>81</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>81</v>
@@ -6920,13 +6926,13 @@
         <v>81</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>81</v>
@@ -6944,19 +6950,19 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>81</v>
@@ -6965,10 +6971,10 @@
         <v>81</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>81</v>
@@ -6979,10 +6985,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6993,7 +6999,7 @@
         <v>79</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>81</v>
@@ -7005,16 +7011,16 @@
         <v>81</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7064,45 +7070,45 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7113,7 +7119,7 @@
         <v>79</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>81</v>
@@ -7125,16 +7131,16 @@
         <v>81</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7184,45 +7190,45 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7245,19 +7251,19 @@
         <v>81</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>81</v>
@@ -7306,7 +7312,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -7318,7 +7324,7 @@
         <v>81</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>81</v>
@@ -7327,10 +7333,10 @@
         <v>81</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>81</v>
@@ -7341,10 +7347,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7355,7 +7361,7 @@
         <v>79</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>81</v>
@@ -7367,13 +7373,13 @@
         <v>81</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>212</v>
+        <v>234</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7424,13 +7430,13 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>81</v>
@@ -7448,7 +7454,7 @@
         <v>81</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>81</v>
@@ -7459,14 +7465,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7485,16 +7491,16 @@
         <v>81</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7544,7 +7550,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7556,7 +7562,7 @@
         <v>81</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>81</v>
@@ -7568,7 +7574,7 @@
         <v>81</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>81</v>
@@ -7579,14 +7585,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7599,25 +7605,25 @@
         <v>81</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>81</v>
@@ -7666,7 +7672,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7678,7 +7684,7 @@
         <v>81</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>81</v>
@@ -7690,7 +7696,7 @@
         <v>81</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>81</v>
@@ -7701,10 +7707,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7715,7 +7721,7 @@
         <v>79</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>81</v>
@@ -7727,13 +7733,13 @@
         <v>81</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7784,19 +7790,19 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>81</v>
@@ -7805,10 +7811,10 @@
         <v>81</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>81</v>
@@ -7819,10 +7825,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7833,7 +7839,7 @@
         <v>79</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>81</v>
@@ -7845,13 +7851,13 @@
         <v>81</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7902,19 +7908,19 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>81</v>
@@ -7923,10 +7929,10 @@
         <v>81</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>81</v>
@@ -7937,10 +7943,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7951,7 +7957,7 @@
         <v>79</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>81</v>
@@ -7963,19 +7969,19 @@
         <v>81</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>81</v>
@@ -8000,13 +8006,13 @@
         <v>81</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>81</v>
@@ -8024,31 +8030,31 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>81</v>
@@ -8059,10 +8065,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8085,19 +8091,19 @@
         <v>81</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>81</v>
@@ -8122,13 +8128,13 @@
         <v>81</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>81</v>
@@ -8146,7 +8152,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -8158,19 +8164,19 @@
         <v>81</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>81</v>
@@ -8181,10 +8187,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8195,7 +8201,7 @@
         <v>79</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>81</v>
@@ -8207,17 +8213,17 @@
         <v>81</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>81</v>
@@ -8266,19 +8272,19 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>81</v>
@@ -8290,7 +8296,7 @@
         <v>81</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>81</v>
@@ -8301,10 +8307,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8315,7 +8321,7 @@
         <v>79</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>81</v>
@@ -8327,13 +8333,13 @@
         <v>81</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>212</v>
+        <v>234</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8384,19 +8390,19 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>81</v>
@@ -8405,10 +8411,10 @@
         <v>81</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>81</v>
@@ -8419,10 +8425,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8442,19 +8448,19 @@
         <v>81</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8504,7 +8510,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8516,7 +8522,7 @@
         <v>81</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>81</v>
@@ -8525,10 +8531,10 @@
         <v>81</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>81</v>
@@ -8539,10 +8545,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8550,10 +8556,10 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>81</v>
@@ -8562,19 +8568,19 @@
         <v>81</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8624,7 +8630,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8636,7 +8642,7 @@
         <v>81</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>81</v>
@@ -8645,10 +8651,10 @@
         <v>81</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>81</v>
@@ -8659,10 +8665,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8682,22 +8688,22 @@
         <v>81</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>81</v>
@@ -8746,7 +8752,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8758,7 +8764,7 @@
         <v>81</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>103</v>
+        <v>502</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>81</v>
@@ -8767,10 +8773,10 @@
         <v>81</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>81</v>
@@ -8781,10 +8787,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8795,7 +8801,7 @@
         <v>79</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>81</v>
@@ -8807,13 +8813,13 @@
         <v>81</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>212</v>
+        <v>234</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8864,13 +8870,13 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>81</v>
@@ -8888,7 +8894,7 @@
         <v>81</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>81</v>
@@ -8899,14 +8905,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8925,16 +8931,16 @@
         <v>81</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8984,7 +8990,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8996,7 +9002,7 @@
         <v>81</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>81</v>
@@ -9008,7 +9014,7 @@
         <v>81</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>81</v>
@@ -9019,14 +9025,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -9039,25 +9045,25 @@
         <v>81</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>81</v>
@@ -9106,7 +9112,7 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -9118,7 +9124,7 @@
         <v>81</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>81</v>
@@ -9130,7 +9136,7 @@
         <v>81</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>81</v>
@@ -9141,10 +9147,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9152,10 +9158,10 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>81</v>
@@ -9164,22 +9170,22 @@
         <v>81</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>81</v>
@@ -9204,13 +9210,13 @@
         <v>81</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>81</v>
@@ -9228,34 +9234,34 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>81</v>
@@ -9263,10 +9269,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9277,7 +9283,7 @@
         <v>79</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>81</v>
@@ -9286,22 +9292,22 @@
         <v>81</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>81</v>
@@ -9350,45 +9356,45 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9399,7 +9405,7 @@
         <v>79</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>81</v>
@@ -9411,19 +9417,19 @@
         <v>81</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>81</v>
@@ -9448,13 +9454,13 @@
         <v>81</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>81</v>
@@ -9472,19 +9478,19 @@
         <v>81</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>81</v>
@@ -9493,10 +9499,10 @@
         <v>81</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>81</v>
@@ -9507,14 +9513,14 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -9533,19 +9539,19 @@
         <v>81</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>81</v>
@@ -9570,13 +9576,13 @@
         <v>81</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>81</v>
@@ -9594,7 +9600,7 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9606,33 +9612,33 @@
         <v>81</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9658,16 +9664,16 @@
         <v>82</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>81</v>
@@ -9716,7 +9722,7 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9728,7 +9734,7 @@
         <v>81</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>81</v>
@@ -9737,10 +9743,10 @@
         <v>81</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>81</v>

--- a/branches/Richard/StructureDefinition-viral-load-log.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-log.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:00:51+00:00</t>
+    <t>2023-05-09T15:03:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-log.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-log.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2493" uniqueCount="528">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2494" uniqueCount="526">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:03:02+00:00</t>
+    <t>2023-05-09T15:34:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -93,7 +93,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.3.0</t>
+    <t>4.0.1</t>
   </si>
   <si>
     <t>Kind</t>
@@ -290,9 +290,6 @@
     <t>Observation[classCode=OBS, moodCode=EVN]</t>
   </si>
   <si>
-    <t>clinical.diagnostics</t>
-  </si>
-  <si>
     <t>Observation.id</t>
   </si>
   <si>
@@ -376,7 +373,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>IETF language tag</t>
+    <t>A human language.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages</t>
@@ -434,10 +431,6 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
-</t>
-  </si>
-  <si>
     <t>N/A</t>
   </si>
   <si>
@@ -478,7 +471,7 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -558,7 +551,7 @@
     <t>A larger event of which this particular Observation is a component or step.  For example,  an observation as part of a procedure.</t>
   </si>
   <si>
-    <t>To link an Observation to an Encounter use `encounter`.  See the  [Notes](http://hl7.org/fhir/R4B/observation.html#obsgrouping) below for guidance on referencing another Observation.</t>
+    <t>To link an Observation to an Encounter use `encounter`.  See the  [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below for guidance on referencing another Observation.</t>
   </si>
   <si>
     <t>Event.partOf</t>
@@ -591,7 +584,7 @@
     <t>Codes providing the status of an observation.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-status|4.3.0</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-status|4.0.1</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -683,6 +676,10 @@
     <t>Observation.code.id</t>
   </si>
   <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
     <t>Unique id for inter-element referencing</t>
   </si>
   <si>
@@ -745,10 +742,6 @@
     <t>Observation.code.text</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
     <t>Plain text representation of the concept</t>
   </si>
   <si>
@@ -776,7 +769,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Group|Device|Location|Organization|Procedure|Practitioner|Medication|Substance)
+    <t xml:space="preserve">Reference(Patient|Group|Device|Location)
 </t>
   </si>
   <si>
@@ -817,7 +810,7 @@
     <t>The actual focus of an observation when it is not the patient of record representing something or someone associated with the patient such as a spouse, parent, fetus, or donor. For example, fetus observations in a mother's record.  The focus of an observation could also be an existing condition,  an intervention, the subject's diet,  another observation of the subject,  or a body structure such as tumor or implanted device.   An example use case would be using the Observation resource to capture whether the mother is trained to change her child's tracheostomy tube. In this example, the child is the patient of record and the mother is the focus.</t>
   </si>
   <si>
-    <t>Typically, an observation is made about the subject - a patient, or group of patients, location, or device - and the distinction between the subject and what is directly measured for an observation is specified in the observation code itself ( e.g., "Blood Glucose") and does not need to be represented separately using this element.  Use `specimen` if a reference to a specimen is required.  If a code is required instead of a resource use either  `bodysite` for bodysites or the standard extension [focusCode](http://hl7.org/fhir/R4B/extension-observation-focuscode.html).</t>
+    <t>Typically, an observation is made about the subject - a patient, or group of patients, location, or device - and the distinction between the subject and what is directly measured for an observation is specified in the observation code itself ( e.g., "Blood Glucose") and does not need to be represented separately using this element.  Use `specimen` if a reference to a specimen is required.  If a code is required instead of a resource use either  `bodysite` for bodysites or the standard extension [focusCode](http://hl7.org/fhir/R4/extension-observation-focuscode.html).</t>
   </si>
   <si>
     <t>participation[typeCode=SBJ]</t>
@@ -875,7 +868,7 @@
     <t>The time or time-period the observed value is asserted as being true. For biological subjects - e.g. human patients - this is usually called the "physiologically relevant time". This is usually either the time of the procedure or of specimen collection, but very often the source of the date/time is not known, only the date/time itself.</t>
   </si>
   <si>
-    <t>At least a date should be present unless this observation is a historical report.  For recording imprecise or "fuzzy" times (For example, a blood glucose measurement taken "after breakfast") use the [Timing](http://hl7.org/fhir/R4B/datatypes.html#timing) datatype which allow the measurement to be tied to regular life events.</t>
+    <t>At least a date should be present unless this observation is a historical report.  For recording imprecise or "fuzzy" times (For example, a blood glucose measurement taken "after breakfast") use the [Timing](http://hl7.org/fhir/R4/datatypes.html#timing) datatype which allow the measurement to be tied to regular life events.</t>
   </si>
   <si>
     <t>Knowing when an observation was deemed true is important to its relevance as well as determining trends.</t>
@@ -919,7 +912,7 @@
     <t>The date and time this version of the observation was made available to providers, typically after the results have been reviewed and verified.</t>
   </si>
   <si>
-    <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/R4B/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
+    <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/R4/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
   </si>
   <si>
     <t>OBR.22 (or MSH.7), or perhaps OBX-19 (depends on who observation made)</t>
@@ -972,7 +965,7 @@
     <t>The information determined as a result of making the observation, if the information has a simple value.</t>
   </si>
   <si>
-    <t>An observation may have; 1)  a single value here, 2)  both a value and a set of related or component values,  or 3)  only a set of related or component values. If a value is present, the datatype for this element should be determined by Observation.code.  A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4B/observation.html#notes) below.</t>
+    <t>An observation may have; 1)  a single value here, 2)  both a value and a set of related or component values,  or 3)  only a set of related or component values. If a value is present, the datatype for this element should be determined by Observation.code.  A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
   </si>
   <si>
     <t>An observation exists to have a value, though it might not if it is in error, or if it represents a group of observations.</t>
@@ -1061,7 +1054,10 @@
     <t>If there is no comparator, then there is no modification of the value</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/quantity-comparator|4.3.0</t>
+    <t>How the Quantity should be understood and represented.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/quantity-comparator|4.0.1</t>
   </si>
   <si>
     <t>Quantity.comparator</t>
@@ -1250,13 +1246,13 @@
   </si>
   <si>
     <t>Only used if not implicit in code found in Observation.code.  In many systems, this may be represented as a related observation instead of an inline component.   
-If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4B/extension-bodysite.html).</t>
+If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
   </si>
   <si>
     <t>example</t>
   </si>
   <si>
-    <t>SNOMED CT Body site concepts</t>
+    <t>Codes describing anatomical locations. May include laterality.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/body-site</t>
@@ -1376,7 +1372,7 @@
     <t>Knowing what values are considered "normal" can help evaluate the significance of a particular result. Need to be able to provide multiple reference ranges for different contexts.</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 obs-3:Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
   </si>
   <si>
@@ -1542,7 +1538,7 @@
     <t>This observation is a group observation (e.g. a battery, a panel of tests, a set of vital sign measurements) that includes the target as a member of the group.</t>
   </si>
   <si>
-    <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4B/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](http://hl7.org/fhir/R4B/questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
+    <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](http://hl7.org/fhir/R4/questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
   </si>
   <si>
     <t>Relationships established by OBX-4 usage</t>
@@ -1564,7 +1560,7 @@
     <t>The target resource that represents a measurement from which this observation value is derived. For example, a calculated anion gap or a fetal measurement based on an ultrasound image.</t>
   </si>
   <si>
-    <t>All the reference choices that are listed in this element can represent clinical observations and other measurements that may be the source for a derived value.  The most common reference will be another Observation.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4B/observation.html#obsgrouping) below.</t>
+    <t>All the reference choices that are listed in this element can represent clinical observations and other measurements that may be the source for a derived value.  The most common reference will be another Observation.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.</t>
   </si>
   <si>
     <t>.targetObservation</t>
@@ -1579,14 +1575,10 @@
     <t>Some observations have multiple component observations.  These component observations are expressed as separate code value pairs that share the same attributes.  Examples include systolic and diastolic component observations for blood pressure measurement and multiple component observations for genetics observations.</t>
   </si>
   <si>
-    <t>For a discussion on the ways Observations can be assembled in groups together see [Notes](http://hl7.org/fhir/R4B/observation.html#notes) below.</t>
+    <t>For a discussion on the ways Observations can be assembled in groups together see [Notes](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
   </si>
   <si>
     <t>Component observations share the same attributes in the Observation resource as the primary observation and are always treated a part of a single observation (they are not separable).   However, the reference range for the primary observation value is not inherited by the component values and is required when appropriate for each component observation.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
-</t>
   </si>
   <si>
     <t>containment by OBX-4?</t>
@@ -1636,7 +1628,7 @@
     <t>Actual component result</t>
   </si>
   <si>
-    <t>Used when observation has a set of component observations. An observation may have both a value (e.g. an  Apgar score)  and component observations (the observations from which the Apgar score was derived). If a value is present, the datatype for this element should be determined by Observation.code. A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4B/observation.html#notes) below.</t>
+    <t>Used when observation has a set of component observations. An observation may have both a value (e.g. an  Apgar score)  and component observations (the observations from which the Apgar score was derived). If a value is present, the datatype for this element should be determined by Observation.code. A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
   </si>
   <si>
     <t>363714003 |Interprets| &lt; 441742003 |Evaluation finding|</t>
@@ -2269,7 +2261,7 @@
         <v>89</v>
       </c>
       <c r="AO2" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AP2" t="s" s="2">
         <v>81</v>
@@ -2277,10 +2269,10 @@
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -2291,28 +2283,28 @@
         <v>79</v>
       </c>
       <c r="G3" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J3" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="H3" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I3" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J3" t="s" s="2">
+      <c r="K3" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="K3" t="s" s="2">
+      <c r="L3" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="L3" t="s" s="2">
+      <c r="M3" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="M3" t="s" s="2">
+      <c r="N3" t="s" s="2">
         <v>96</v>
-      </c>
-      <c r="N3" t="s" s="2">
-        <v>97</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -2362,13 +2354,13 @@
         <v>81</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>81</v>
@@ -2397,10 +2389,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2411,25 +2403,25 @@
         <v>79</v>
       </c>
       <c r="G4" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H4" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I4" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J4" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="H4" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I4" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J4" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="K4" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="L4" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="L4" t="s" s="2">
+      <c r="M4" t="s" s="2">
         <v>101</v>
-      </c>
-      <c r="M4" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2480,19 +2472,19 @@
         <v>81</v>
       </c>
       <c r="AF4" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AG4" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH4" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI4" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ4" t="s" s="2">
         <v>103</v>
-      </c>
-      <c r="AG4" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH4" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI4" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ4" t="s" s="2">
-        <v>104</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>81</v>
@@ -2515,10 +2507,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2529,28 +2521,28 @@
         <v>79</v>
       </c>
       <c r="G5" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H5" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I5" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="H5" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I5" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="J5" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L5" t="s" s="2">
         <v>106</v>
       </c>
-      <c r="L5" t="s" s="2">
+      <c r="M5" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="M5" t="s" s="2">
+      <c r="N5" t="s" s="2">
         <v>108</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>109</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2600,19 +2592,19 @@
         <v>81</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>81</v>
@@ -2635,10 +2627,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2649,7 +2641,7 @@
         <v>79</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>81</v>
@@ -2661,16 +2653,16 @@
         <v>81</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="M6" t="s" s="2">
+      <c r="N6" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>115</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2696,43 +2688,43 @@
         <v>81</v>
       </c>
       <c r="X6" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="Y6" t="s" s="2">
         <v>116</v>
       </c>
-      <c r="Y6" t="s" s="2">
+      <c r="Z6" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="Z6" t="s" s="2">
+      <c r="AA6" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE6" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF6" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="AA6" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>119</v>
-      </c>
       <c r="AG6" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>81</v>
@@ -2755,21 +2747,21 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>81</v>
@@ -2781,16 +2773,16 @@
         <v>81</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="L7" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="L7" t="s" s="2">
+      <c r="M7" t="s" s="2">
         <v>123</v>
       </c>
-      <c r="M7" t="s" s="2">
+      <c r="N7" t="s" s="2">
         <v>124</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>125</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2840,31 +2832,31 @@
         <v>81</v>
       </c>
       <c r="AF7" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="AG7" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH7" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI7" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ7" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK7" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL7" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM7" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN7" t="s" s="2">
         <v>126</v>
-      </c>
-      <c r="AG7" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH7" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI7" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ7" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK7" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL7" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM7" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN7" t="s" s="2">
-        <v>127</v>
       </c>
       <c r="AO7" t="s" s="2">
         <v>81</v>
@@ -2875,14 +2867,14 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2901,16 +2893,16 @@
         <v>81</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>130</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>131</v>
       </c>
-      <c r="M8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>132</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>133</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2960,7 +2952,7 @@
         <v>81</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>79</v>
@@ -2972,7 +2964,7 @@
         <v>81</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>135</v>
+        <v>81</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>81</v>
@@ -2984,7 +2976,7 @@
         <v>81</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="AO8" t="s" s="2">
         <v>81</v>
@@ -2995,14 +2987,14 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -3021,16 +3013,16 @@
         <v>81</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="L9" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="M9" t="s" s="2">
         <v>139</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="N9" t="s" s="2">
         <v>140</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>142</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -3080,7 +3072,7 @@
         <v>81</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>79</v>
@@ -3092,7 +3084,7 @@
         <v>81</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>81</v>
@@ -3104,7 +3096,7 @@
         <v>81</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="AO9" t="s" s="2">
         <v>81</v>
@@ -3115,14 +3107,14 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -3135,25 +3127,25 @@
         <v>81</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>81</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="L10" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="M10" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="N10" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O10" t="s" s="2">
         <v>146</v>
-      </c>
-      <c r="M10" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>148</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>81</v>
@@ -3202,7 +3194,7 @@
         <v>81</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>79</v>
@@ -3214,7 +3206,7 @@
         <v>81</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>81</v>
@@ -3226,7 +3218,7 @@
         <v>81</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="AO10" t="s" s="2">
         <v>81</v>
@@ -3237,10 +3229,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3260,20 +3252,20 @@
         <v>81</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L11" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="M11" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="L11" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>153</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>81</v>
@@ -3322,7 +3314,7 @@
         <v>81</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>79</v>
@@ -3334,22 +3326,22 @@
         <v>81</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK11" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AL11" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM11" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="AN11" t="s" s="2">
         <v>155</v>
       </c>
-      <c r="AL11" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM11" t="s" s="2">
+      <c r="AO11" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="AN11" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="AO11" t="s" s="2">
-        <v>158</v>
       </c>
       <c r="AP11" t="s" s="2">
         <v>81</v>
@@ -3357,14 +3349,14 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -3380,20 +3372,20 @@
         <v>81</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L12" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="M12" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="L12" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>81</v>
@@ -3442,7 +3434,7 @@
         <v>81</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>79</v>
@@ -3454,19 +3446,19 @@
         <v>81</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AL12" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM12" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AN12" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AL12" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM12" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="AN12" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>81</v>
@@ -3477,14 +3469,14 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -3500,19 +3492,19 @@
         <v>81</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="L13" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="M13" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>171</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>173</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3562,7 +3554,7 @@
         <v>81</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>79</v>
@@ -3574,19 +3566,19 @@
         <v>81</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK13" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="AL13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM13" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="AN13" t="s" s="2">
         <v>174</v>
-      </c>
-      <c r="AL13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM13" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="AN13" t="s" s="2">
-        <v>176</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>81</v>
@@ -3597,10 +3589,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3608,34 +3600,34 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="G14" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H14" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I14" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="G14" t="s" s="2">
+      <c r="J14" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="H14" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I14" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="J14" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="K14" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="M14" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="N14" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="O14" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>181</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>81</v>
@@ -3660,58 +3652,58 @@
         <v>81</v>
       </c>
       <c r="X14" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="Y14" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="Z14" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="Y14" t="s" s="2">
+      <c r="AA14" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB14" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC14" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD14" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE14" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF14" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AG14" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AH14" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI14" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ14" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK14" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="Z14" t="s" s="2">
+      <c r="AL14" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="AA14" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB14" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC14" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD14" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE14" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF14" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="AG14" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AH14" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI14" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ14" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK14" t="s" s="2">
+      <c r="AM14" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="AL14" t="s" s="2">
+      <c r="AN14" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="AM14" t="s" s="2">
+      <c r="AO14" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="AN14" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="AO14" t="s" s="2">
-        <v>189</v>
       </c>
       <c r="AP14" t="s" s="2">
         <v>81</v>
@@ -3719,10 +3711,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3745,19 +3737,19 @@
         <v>81</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="O15" t="s" s="2">
         <v>193</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>195</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>81</v>
@@ -3782,13 +3774,13 @@
         <v>81</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>81</v>
@@ -3806,7 +3798,7 @@
         <v>81</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
@@ -3818,7 +3810,7 @@
         <v>81</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>81</v>
@@ -3830,10 +3822,10 @@
         <v>81</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>81</v>
@@ -3841,45 +3833,45 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="G16" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H16" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I16" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J16" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="G16" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="H16" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I16" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J16" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="K16" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="L16" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="M16" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="N16" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="O16" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>205</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>81</v>
@@ -3904,67 +3896,67 @@
         <v>81</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="AA16" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF16" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="AG16" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AH16" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI16" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ16" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK16" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="AL16" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="AA16" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="AG16" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AH16" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI16" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ16" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK16" t="s" s="2">
+      <c r="AM16" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="AL16" t="s" s="2">
+      <c r="AN16" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="AM16" t="s" s="2">
+      <c r="AO16" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="AN16" t="s" s="2">
+      <c r="AP16" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="AO16" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="AP16" t="s" s="2">
-        <v>212</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3975,7 +3967,7 @@
         <v>79</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>81</v>
@@ -3987,13 +3979,13 @@
         <v>81</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>94</v>
+        <v>212</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>215</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4044,31 +4036,31 @@
         <v>81</v>
       </c>
       <c r="AF17" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AG17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH17" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI17" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ17" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK17" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL17" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM17" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN17" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AG17" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH17" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI17" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ17" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AK17" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL17" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM17" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN17" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>81</v>
@@ -4079,14 +4071,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -4105,16 +4097,16 @@
         <v>81</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="M18" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="N18" t="s" s="2">
         <v>140</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>142</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4152,19 +4144,19 @@
         <v>81</v>
       </c>
       <c r="AB18" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="AC18" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="AC18" t="s" s="2">
+      <c r="AD18" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE18" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="AD18" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE18" t="s" s="2">
+      <c r="AF18" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="AF18" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -4176,7 +4168,7 @@
         <v>81</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>81</v>
@@ -4188,7 +4180,7 @@
         <v>81</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>81</v>
@@ -4199,10 +4191,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4222,22 +4214,22 @@
         <v>81</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="N19" t="s" s="2">
+      <c r="O19" t="s" s="2">
         <v>228</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>229</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>81</v>
@@ -4286,7 +4278,7 @@
         <v>81</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -4298,7 +4290,7 @@
         <v>81</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>81</v>
@@ -4307,10 +4299,10 @@
         <v>81</v>
       </c>
       <c r="AM19" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AN19" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>232</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>81</v>
@@ -4321,10 +4313,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4335,31 +4327,31 @@
         <v>79</v>
       </c>
       <c r="G20" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H20" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I20" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J20" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="H20" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I20" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J20" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="K20" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="O20" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>81</v>
@@ -4369,70 +4361,70 @@
         <v>81</v>
       </c>
       <c r="S20" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="T20" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U20" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V20" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W20" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X20" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y20" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z20" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA20" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB20" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC20" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD20" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE20" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF20" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="AG20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH20" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI20" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK20" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM20" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="T20" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U20" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V20" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W20" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X20" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y20" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z20" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA20" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB20" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC20" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD20" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE20" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF20" t="s" s="2">
+      <c r="AN20" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="AG20" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH20" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI20" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ20" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK20" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL20" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM20" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="AN20" t="s" s="2">
-        <v>242</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>81</v>
@@ -4443,10 +4435,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4454,34 +4446,34 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="G21" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H21" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I21" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J21" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="G21" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="H21" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I21" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J21" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="K21" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="O21" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>248</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>81</v>
@@ -4530,34 +4522,34 @@
         <v>81</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM21" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AN21" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="AL21" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM21" t="s" s="2">
+      <c r="AO21" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="AO21" t="s" s="2">
-        <v>252</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>81</v>
@@ -4565,10 +4557,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4588,19 +4580,19 @@
         <v>81</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="L22" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4650,7 +4642,7 @@
         <v>81</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -4662,7 +4654,7 @@
         <v>81</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>81</v>
@@ -4671,13 +4663,13 @@
         <v>81</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>81</v>
@@ -4685,45 +4677,45 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="G23" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H23" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I23" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J23" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="G23" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="H23" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I23" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J23" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="K23" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="O23" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>81</v>
@@ -4772,34 +4764,34 @@
         <v>81</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM23" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="AN23" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="AL23" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM23" t="s" s="2">
+      <c r="AO23" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="AO23" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>81</v>
@@ -4807,45 +4799,45 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="G24" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H24" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I24" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J24" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="G24" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="H24" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I24" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J24" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="K24" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>81</v>
@@ -4882,44 +4874,44 @@
         <v>81</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="AC24" s="2"/>
       <c r="AD24" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE24" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AF24" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="AG24" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH24" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI24" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK24" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="AL24" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM24" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="AF24" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="AG24" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH24" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI24" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ24" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK24" t="s" s="2">
+      <c r="AN24" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="AL24" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM24" t="s" s="2">
+      <c r="AO24" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="AO24" t="s" s="2">
-        <v>282</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>81</v>
@@ -4927,47 +4919,47 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="D25" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="G25" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H25" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I25" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J25" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="G25" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="H25" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I25" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J25" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="K25" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="L25" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>81</v>
@@ -5016,34 +5008,34 @@
         <v>81</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM25" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AN25" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="AL25" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM25" t="s" s="2">
+      <c r="AO25" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>282</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>81</v>
@@ -5051,10 +5043,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5065,28 +5057,28 @@
         <v>79</v>
       </c>
       <c r="G26" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H26" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I26" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J26" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="H26" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I26" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J26" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="K26" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>289</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -5136,19 +5128,19 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>81</v>
@@ -5157,13 +5149,13 @@
         <v>81</v>
       </c>
       <c r="AM26" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="AN26" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="AO26" t="s" s="2">
         <v>290</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="AO26" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>81</v>
@@ -5171,10 +5163,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5182,7 +5174,7 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>80</v>
@@ -5194,20 +5186,20 @@
         <v>81</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="L27" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>296</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>81</v>
@@ -5256,7 +5248,7 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -5268,22 +5260,22 @@
         <v>81</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM27" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="AN27" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="AL27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM27" t="s" s="2">
+      <c r="AO27" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="AO27" t="s" s="2">
-        <v>301</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>81</v>
@@ -5291,10 +5283,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5302,34 +5294,34 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="G28" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H28" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I28" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J28" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="G28" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="H28" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I28" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J28" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="K28" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="O28" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>81</v>
@@ -5366,92 +5358,92 @@
         <v>81</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="AC28" s="2"/>
       <c r="AD28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AI28" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK28" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL28" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AM28" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="AJ28" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK28" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL28" t="s" s="2">
+      <c r="AN28" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="AM28" t="s" s="2">
+      <c r="AO28" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP28" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="AO28" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP28" t="s" s="2">
-        <v>312</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="G29" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J29" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="G29" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="H29" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I29" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J29" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="K29" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>81</v>
@@ -5500,45 +5492,45 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AI29" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AM29" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="AJ29" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK29" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL29" t="s" s="2">
+      <c r="AN29" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="AM29" t="s" s="2">
+      <c r="AO29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP29" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="AO29" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP29" t="s" s="2">
-        <v>312</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5549,7 +5541,7 @@
         <v>79</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>81</v>
@@ -5561,13 +5553,13 @@
         <v>81</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>94</v>
+        <v>212</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>215</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5618,31 +5610,31 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AG30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH30" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI30" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK30" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM30" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN30" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AG30" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH30" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI30" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ30" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AK30" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL30" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>81</v>
@@ -5653,14 +5645,14 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5679,16 +5671,16 @@
         <v>81</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="M31" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="N31" t="s" s="2">
         <v>140</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>142</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5726,19 +5718,19 @@
         <v>81</v>
       </c>
       <c r="AB31" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="AC31" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="AC31" t="s" s="2">
+      <c r="AD31" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE31" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="AD31" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE31" t="s" s="2">
+      <c r="AF31" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="AF31" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5750,7 +5742,7 @@
         <v>81</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>81</v>
@@ -5762,7 +5754,7 @@
         <v>81</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>81</v>
@@ -5773,10 +5765,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5784,34 +5776,34 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="G32" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H32" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I32" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J32" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="G32" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="H32" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I32" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J32" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="K32" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="O32" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>81</v>
@@ -5860,31 +5852,31 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="AG32" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH32" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI32" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK32" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM32" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="AN32" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="AG32" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH32" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI32" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ32" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK32" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL32" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>328</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>81</v>
@@ -5895,10 +5887,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5909,102 +5901,104 @@
         <v>79</v>
       </c>
       <c r="G33" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H33" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I33" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="H33" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I33" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="J33" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="P33" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q33" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="R33" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S33" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T33" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U33" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V33" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W33" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X33" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="Y33" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="P33" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q33" t="s" s="2">
+      <c r="Z33" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="R33" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S33" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T33" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U33" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V33" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W33" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X33" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="Y33" s="2"/>
-      <c r="Z33" t="s" s="2">
+      <c r="AA33" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF33" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="AA33" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB33" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC33" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD33" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE33" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF33" t="s" s="2">
+      <c r="AG33" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH33" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI33" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ33" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK33" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM33" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="AG33" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH33" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI33" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ33" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK33" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL33" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM33" t="s" s="2">
+      <c r="AN33" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>338</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>81</v>
@@ -6015,10 +6009,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="B34" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="B34" t="s" s="2">
-        <v>340</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6029,29 +6023,29 @@
         <v>79</v>
       </c>
       <c r="G34" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J34" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="H34" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I34" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J34" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="K34" t="s" s="2">
-        <v>234</v>
+        <v>212</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>342</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>81</v>
@@ -6100,31 +6094,31 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="AG34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH34" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM34" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="AG34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH34" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI34" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ34" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK34" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL34" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM34" t="s" s="2">
+      <c r="AN34" t="s" s="2">
         <v>345</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>346</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>81</v>
@@ -6135,10 +6129,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="B35" t="s" s="2">
         <v>347</v>
-      </c>
-      <c r="B35" t="s" s="2">
-        <v>348</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6149,29 +6143,29 @@
         <v>79</v>
       </c>
       <c r="G35" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J35" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="H35" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I35" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J35" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="K35" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>81</v>
@@ -6220,31 +6214,31 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="AG35" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH35" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI35" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="AG35" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH35" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI35" t="s" s="2">
+      <c r="AJ35" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM35" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="AN35" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="AJ35" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK35" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL35" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="AN35" t="s" s="2">
-        <v>354</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>81</v>
@@ -6255,10 +6249,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="B36" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="B36" t="s" s="2">
-        <v>356</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6269,31 +6263,31 @@
         <v>79</v>
       </c>
       <c r="G36" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J36" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="H36" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I36" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J36" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="K36" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="N36" t="s" s="2">
+      <c r="O36" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>81</v>
@@ -6342,31 +6336,31 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="AG36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH36" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="AN36" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="AG36" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH36" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI36" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ36" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK36" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL36" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>362</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>81</v>
@@ -6377,10 +6371,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6391,7 +6385,7 @@
         <v>79</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>81</v>
@@ -6403,19 +6397,19 @@
         <v>81</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="N37" t="s" s="2">
+      <c r="O37" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>367</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>81</v>
@@ -6440,55 +6434,55 @@
         <v>81</v>
       </c>
       <c r="X37" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="Y37" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="Y37" t="s" s="2">
+      <c r="Z37" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="Z37" t="s" s="2">
+      <c r="AA37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF37" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="AG37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH37" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI37" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="AA37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF37" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="AG37" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH37" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI37" t="s" s="2">
+      <c r="AJ37" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="AN37" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="AJ37" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM37" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>81</v>
@@ -6499,14 +6493,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6525,19 +6519,19 @@
         <v>81</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="N38" t="s" s="2">
+      <c r="O38" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>378</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>81</v>
@@ -6562,14 +6556,14 @@
         <v>81</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="Y38" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="Z38" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="Z38" t="s" s="2">
-        <v>380</v>
-      </c>
       <c r="AA38" t="s" s="2">
         <v>81</v>
       </c>
@@ -6586,7 +6580,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6598,33 +6592,33 @@
         <v>81</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL38" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AM38" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="AM38" t="s" s="2">
+      <c r="AN38" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="AN38" t="s" s="2">
+      <c r="AO38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP38" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="AO38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP38" t="s" s="2">
-        <v>384</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6638,7 +6632,7 @@
         <v>80</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>81</v>
@@ -6647,19 +6641,19 @@
         <v>81</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="N39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>390</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>81</v>
@@ -6708,7 +6702,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6720,7 +6714,7 @@
         <v>81</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>81</v>
@@ -6729,10 +6723,10 @@
         <v>81</v>
       </c>
       <c r="AM39" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="AN39" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>392</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>81</v>
@@ -6743,10 +6737,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6757,7 +6751,7 @@
         <v>79</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>81</v>
@@ -6769,16 +6763,16 @@
         <v>81</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>395</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>396</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6804,69 +6798,69 @@
         <v>81</v>
       </c>
       <c r="X40" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="Y40" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="Y40" t="s" s="2">
+      <c r="Z40" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="Z40" t="s" s="2">
+      <c r="AA40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF40" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AG40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH40" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL40" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="AA40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF40" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="AG40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH40" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ40" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL40" t="s" s="2">
+      <c r="AM40" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="AM40" t="s" s="2">
+      <c r="AN40" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="AN40" t="s" s="2">
+      <c r="AO40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP40" t="s" s="2">
         <v>402</v>
-      </c>
-      <c r="AO40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP40" t="s" s="2">
-        <v>403</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6877,7 +6871,7 @@
         <v>79</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>81</v>
@@ -6889,19 +6883,19 @@
         <v>81</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="N41" t="s" s="2">
+      <c r="O41" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>408</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>81</v>
@@ -6926,55 +6920,55 @@
         <v>81</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Y41" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="Z41" t="s" s="2">
         <v>409</v>
       </c>
-      <c r="Z41" t="s" s="2">
+      <c r="AA41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF41" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AG41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH41" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM41" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="AA41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF41" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="AG41" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH41" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ41" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM41" t="s" s="2">
+      <c r="AN41" t="s" s="2">
         <v>411</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>412</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>81</v>
@@ -6985,10 +6979,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6999,7 +6993,7 @@
         <v>79</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>81</v>
@@ -7011,16 +7005,16 @@
         <v>81</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>415</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7070,45 +7064,45 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL42" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AM42" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="AM42" t="s" s="2">
+      <c r="AN42" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="AN42" t="s" s="2">
+      <c r="AO42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP42" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="AO42" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP42" t="s" s="2">
-        <v>421</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7119,7 +7113,7 @@
         <v>79</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>81</v>
@@ -7131,16 +7125,16 @@
         <v>81</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7190,45 +7184,45 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL43" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="AM43" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="AM43" t="s" s="2">
+      <c r="AN43" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="AN43" t="s" s="2">
+      <c r="AO43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP43" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="AO43" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP43" t="s" s="2">
-        <v>430</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7251,19 +7245,19 @@
         <v>81</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="M44" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="N44" t="s" s="2">
+      <c r="O44" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>81</v>
@@ -7312,7 +7306,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -7324,19 +7318,19 @@
         <v>81</v>
       </c>
       <c r="AJ44" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="AK44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM44" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="AK44" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL44" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM44" t="s" s="2">
+      <c r="AN44" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>439</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>81</v>
@@ -7347,10 +7341,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7361,7 +7355,7 @@
         <v>79</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>81</v>
@@ -7373,13 +7367,13 @@
         <v>81</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>234</v>
+        <v>212</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>215</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7430,31 +7424,31 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AG45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH45" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN45" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AG45" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH45" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AK45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN45" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>81</v>
@@ -7465,14 +7459,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7491,16 +7485,16 @@
         <v>81</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="N46" t="s" s="2">
         <v>140</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>142</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7550,7 +7544,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7562,7 +7556,7 @@
         <v>81</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>81</v>
@@ -7574,7 +7568,7 @@
         <v>81</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>81</v>
@@ -7585,14 +7579,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7605,25 +7599,25 @@
         <v>81</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="M47" t="s" s="2">
-        <v>445</v>
-      </c>
       <c r="N47" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>81</v>
@@ -7672,7 +7666,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7684,7 +7678,7 @@
         <v>81</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>81</v>
@@ -7696,7 +7690,7 @@
         <v>81</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>81</v>
@@ -7707,10 +7701,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7721,7 +7715,7 @@
         <v>79</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>81</v>
@@ -7733,13 +7727,13 @@
         <v>81</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="M48" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>450</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7790,31 +7784,31 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AI48" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM48" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="AJ48" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK48" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL48" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM48" t="s" s="2">
+      <c r="AN48" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>81</v>
@@ -7825,10 +7819,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7839,7 +7833,7 @@
         <v>79</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>81</v>
@@ -7851,13 +7845,13 @@
         <v>81</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>456</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7908,31 +7902,31 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AI49" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK49" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM49" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="AJ49" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK49" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL49" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>452</v>
-      </c>
       <c r="AN49" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>81</v>
@@ -7943,10 +7937,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7957,7 +7951,7 @@
         <v>79</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>81</v>
@@ -7969,19 +7963,19 @@
         <v>81</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="N50" t="s" s="2">
+      <c r="O50" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>81</v>
@@ -8006,55 +8000,55 @@
         <v>81</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Y50" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="Z50" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="Z50" t="s" s="2">
+      <c r="AA50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF50" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL50" t="s" s="2">
         <v>464</v>
       </c>
-      <c r="AA50" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB50" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD50" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE50" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF50" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="AG50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH50" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI50" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ50" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK50" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL50" t="s" s="2">
+      <c r="AM50" t="s" s="2">
         <v>465</v>
       </c>
-      <c r="AM50" t="s" s="2">
-        <v>466</v>
-      </c>
       <c r="AN50" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>81</v>
@@ -8065,10 +8059,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8091,19 +8085,19 @@
         <v>81</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>468</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>469</v>
       </c>
-      <c r="N51" t="s" s="2">
+      <c r="O51" t="s" s="2">
         <v>470</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>471</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>81</v>
@@ -8128,14 +8122,14 @@
         <v>81</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Y51" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="Z51" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="Z51" t="s" s="2">
-        <v>473</v>
-      </c>
       <c r="AA51" t="s" s="2">
         <v>81</v>
       </c>
@@ -8152,7 +8146,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -8164,19 +8158,19 @@
         <v>81</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL51" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="AM51" t="s" s="2">
         <v>465</v>
       </c>
-      <c r="AM51" t="s" s="2">
-        <v>466</v>
-      </c>
       <c r="AN51" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>81</v>
@@ -8187,10 +8181,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8201,7 +8195,7 @@
         <v>79</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>81</v>
@@ -8213,17 +8207,17 @@
         <v>81</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="L52" t="s" s="2">
         <v>475</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="M52" t="s" s="2">
         <v>476</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>477</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>81</v>
@@ -8272,19 +8266,19 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>81</v>
@@ -8296,7 +8290,7 @@
         <v>81</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>81</v>
@@ -8307,10 +8301,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8321,7 +8315,7 @@
         <v>79</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>81</v>
@@ -8333,13 +8327,13 @@
         <v>81</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>234</v>
+        <v>212</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>481</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>482</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8390,19 +8384,19 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>81</v>
@@ -8411,10 +8405,10 @@
         <v>81</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>81</v>
@@ -8425,10 +8419,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8448,19 +8442,19 @@
         <v>81</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>485</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
         <v>486</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>487</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>488</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8510,7 +8504,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8522,7 +8516,7 @@
         <v>81</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>81</v>
@@ -8531,10 +8525,10 @@
         <v>81</v>
       </c>
       <c r="AM54" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AN54" t="s" s="2">
         <v>489</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>490</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>81</v>
@@ -8545,10 +8539,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8556,31 +8550,31 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J55" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="G55" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="H55" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I55" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J55" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="K55" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="L55" t="s" s="2">
         <v>492</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="M55" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>495</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8630,7 +8624,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8642,7 +8636,7 @@
         <v>81</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>81</v>
@@ -8651,10 +8645,10 @@
         <v>81</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>81</v>
@@ -8665,10 +8659,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8688,22 +8682,22 @@
         <v>81</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>499</v>
       </c>
-      <c r="N56" t="s" s="2">
+      <c r="O56" t="s" s="2">
         <v>500</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>501</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>81</v>
@@ -8752,7 +8746,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8764,19 +8758,19 @@
         <v>81</v>
       </c>
       <c r="AJ56" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="AN56" t="s" s="2">
         <v>502</v>
-      </c>
-      <c r="AK56" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL56" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="AN56" t="s" s="2">
-        <v>504</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>81</v>
@@ -8787,10 +8781,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8801,7 +8795,7 @@
         <v>79</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>81</v>
@@ -8813,13 +8807,13 @@
         <v>81</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>234</v>
+        <v>212</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>215</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8870,31 +8864,31 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN57" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AG57" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH57" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AK57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>81</v>
@@ -8905,14 +8899,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8931,16 +8925,16 @@
         <v>81</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="N58" t="s" s="2">
         <v>140</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>142</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8990,7 +8984,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -9002,7 +8996,7 @@
         <v>81</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>81</v>
@@ -9014,7 +9008,7 @@
         <v>81</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>81</v>
@@ -9025,14 +9019,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -9045,25 +9039,25 @@
         <v>81</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="M59" t="s" s="2">
-        <v>445</v>
-      </c>
       <c r="N59" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>81</v>
@@ -9112,7 +9106,7 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -9124,7 +9118,7 @@
         <v>81</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>81</v>
@@ -9136,7 +9130,7 @@
         <v>81</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>81</v>
@@ -9147,10 +9141,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9158,34 +9152,34 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J60" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="G60" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="H60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J60" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="K60" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="N60" t="s" s="2">
         <v>509</v>
       </c>
-      <c r="M60" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>511</v>
-      </c>
       <c r="O60" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>81</v>
@@ -9210,58 +9204,58 @@
         <v>81</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Y60" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL60" t="s" s="2">
         <v>512</v>
       </c>
-      <c r="Z60" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="AA60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF60" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="AG60" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AH60" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ60" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>514</v>
-      </c>
       <c r="AM60" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="AO60" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="AO60" t="s" s="2">
-        <v>211</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>81</v>
@@ -9269,10 +9263,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9283,31 +9277,31 @@
         <v>79</v>
       </c>
       <c r="G61" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J61" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="H61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J61" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="K61" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="N61" t="s" s="2">
         <v>516</v>
       </c>
-      <c r="L61" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="M61" t="s" s="2">
+      <c r="O61" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>81</v>
@@ -9356,45 +9350,45 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="AM61" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="AO61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP61" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="AO61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP61" t="s" s="2">
-        <v>312</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9405,7 +9399,7 @@
         <v>79</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>81</v>
@@ -9417,19 +9411,19 @@
         <v>81</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="N62" t="s" s="2">
         <v>521</v>
       </c>
-      <c r="M62" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>523</v>
-      </c>
       <c r="O62" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>81</v>
@@ -9454,55 +9448,55 @@
         <v>81</v>
       </c>
       <c r="X62" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="Y62" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="Y62" t="s" s="2">
+      <c r="Z62" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="Z62" t="s" s="2">
+      <c r="AA62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI62" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="AA62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF62" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="AG62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH62" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI62" t="s" s="2">
+      <c r="AJ62" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="AN62" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="AJ62" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>81</v>
@@ -9513,14 +9507,14 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -9539,19 +9533,19 @@
         <v>81</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="N63" t="s" s="2">
+      <c r="O63" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>378</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>81</v>
@@ -9576,14 +9570,14 @@
         <v>81</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="Y63" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="Z63" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="Z63" t="s" s="2">
-        <v>380</v>
-      </c>
       <c r="AA63" t="s" s="2">
         <v>81</v>
       </c>
@@ -9600,7 +9594,7 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9612,33 +9606,33 @@
         <v>81</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL63" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AM63" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="AM63" t="s" s="2">
+      <c r="AN63" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="AN63" t="s" s="2">
+      <c r="AO63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP63" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="AO63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP63" t="s" s="2">
-        <v>384</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9664,16 +9658,16 @@
         <v>82</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="N64" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="O64" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>81</v>
@@ -9722,7 +9716,7 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9734,7 +9728,7 @@
         <v>81</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>81</v>
@@ -9743,10 +9737,10 @@
         <v>81</v>
       </c>
       <c r="AM64" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="AN64" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>439</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>81</v>

--- a/branches/Richard/StructureDefinition-viral-load-log.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-log.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:34:42+00:00</t>
+    <t>2023-05-09T15:35:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
